--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Testing\flipkart\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CEEFB9-4914-4023-8B11-793A75B8CA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79EE7ECB-EA31-4524-A035-C1C950B4EC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AE0F3E1C-32CA-4FDB-8FB4-626E19483892}"/>
   </bookViews>
@@ -64,13 +64,13 @@
     <t>earphones</t>
   </si>
   <si>
-    <t>JBL C100SI Wired In Ear Headphones</t>
-  </si>
-  <si>
     <t>laptop</t>
   </si>
   <si>
     <t>Apple 2023 MacBook Pro Laptop M2</t>
+  </si>
+  <si>
+    <t>OnePlus Bullets Z2 Bluetooth Wireless</t>
   </si>
 </sst>
 </file>
@@ -482,7 +482,7 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -493,10 +493,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
         <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
